--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Starkey\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Starkey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C144FC29-97C1-42B1-9481-09876970E171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE256A64-F0AC-4B2D-B47C-3562D54B0729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="23295" windowHeight="13380" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Starkey\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Starkey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE256A64-F0AC-4B2D-B47C-3562D54B0729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8352DFBB-E046-4759-9919-11CA32694C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5115,7 +5115,7 @@
         <v>46083.796180555553</v>
       </c>
       <c r="J165">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K165" t="s">
         <v>11</v>
@@ -5144,7 +5144,7 @@
         <v>46083.796180555553</v>
       </c>
       <c r="J166">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K166" t="s">
         <v>11</v>
@@ -5173,7 +5173,7 @@
         <v>46083.796875</v>
       </c>
       <c r="J167">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K167" t="s">
         <v>11</v>
@@ -5202,7 +5202,7 @@
         <v>46083.796875</v>
       </c>
       <c r="J168">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K168" t="s">
         <v>11</v>
@@ -5231,7 +5231,7 @@
         <v>46083.797569444447</v>
       </c>
       <c r="J169">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K169" t="s">
         <v>11</v>
@@ -5260,7 +5260,7 @@
         <v>46083.798263888886</v>
       </c>
       <c r="J170">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K170" t="s">
         <v>11</v>
@@ -5289,7 +5289,7 @@
         <v>46083.798958333333</v>
       </c>
       <c r="J171">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K171" t="s">
         <v>11</v>
@@ -5318,7 +5318,7 @@
         <v>46083.798958333333</v>
       </c>
       <c r="J172">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K172" t="s">
         <v>11</v>
@@ -5347,7 +5347,7 @@
         <v>46083.79965277778</v>
       </c>
       <c r="J173">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K173" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Starkey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8352DFBB-E046-4759-9919-11CA32694C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83F2BD6-5BA7-4DD1-898B-954DEB18657D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Starkey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83F2BD6-5BA7-4DD1-898B-954DEB18657D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725C7C66-2828-496B-B976-4D46E8B41A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="43">
   <si>
     <t>Company Name</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>Travis Burton</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
 </sst>
 </file>
@@ -5354,78 +5357,306 @@
       </c>
     </row>
     <row r="174" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H174" s="2"/>
-      <c r="I174" s="1"/>
+      <c r="B174" t="s">
+        <v>32</v>
+      </c>
+      <c r="C174">
+        <v>2401</v>
+      </c>
+      <c r="D174" t="s">
+        <v>33</v>
+      </c>
+      <c r="F174" t="s">
+        <v>42</v>
+      </c>
+      <c r="G174" t="s">
+        <v>13</v>
+      </c>
+      <c r="H174" s="2">
+        <v>0</v>
+      </c>
+      <c r="I174" s="1">
+        <v>46118.794328703705</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="175" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H175" s="2"/>
-      <c r="I175" s="1"/>
+      <c r="B175" t="s">
+        <v>32</v>
+      </c>
+      <c r="C175">
+        <v>2403</v>
+      </c>
+      <c r="D175" t="s">
+        <v>34</v>
+      </c>
+      <c r="F175" t="s">
+        <v>42</v>
+      </c>
+      <c r="G175" t="s">
+        <v>13</v>
+      </c>
+      <c r="H175" s="2">
+        <v>0</v>
+      </c>
+      <c r="I175" s="1">
+        <v>46118.795023148145</v>
+      </c>
+      <c r="J175">
+        <v>1</v>
+      </c>
+      <c r="K175" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="176" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H176" s="2"/>
-      <c r="I176" s="1"/>
-    </row>
-    <row r="177" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H177" s="2"/>
-      <c r="I177" s="1"/>
-    </row>
-    <row r="178" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H178" s="2"/>
-      <c r="I178" s="1"/>
-    </row>
-    <row r="179" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H179" s="2"/>
-      <c r="I179" s="1"/>
-    </row>
-    <row r="180" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H180" s="2"/>
-      <c r="I180" s="1"/>
-    </row>
-    <row r="181" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H181" s="2"/>
-      <c r="I181" s="1"/>
-    </row>
-    <row r="182" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H182" s="2"/>
-      <c r="I182" s="1"/>
-    </row>
-    <row r="183" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B176" t="s">
+        <v>32</v>
+      </c>
+      <c r="C176">
+        <v>2404</v>
+      </c>
+      <c r="D176" t="s">
+        <v>35</v>
+      </c>
+      <c r="F176" t="s">
+        <v>42</v>
+      </c>
+      <c r="G176" t="s">
+        <v>13</v>
+      </c>
+      <c r="H176" s="2">
+        <v>0</v>
+      </c>
+      <c r="I176" s="1">
+        <v>46118.795023148145</v>
+      </c>
+      <c r="J176">
+        <v>1</v>
+      </c>
+      <c r="K176" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B177" t="s">
+        <v>32</v>
+      </c>
+      <c r="C177">
+        <v>2406</v>
+      </c>
+      <c r="D177" t="s">
+        <v>36</v>
+      </c>
+      <c r="F177" t="s">
+        <v>42</v>
+      </c>
+      <c r="G177" t="s">
+        <v>13</v>
+      </c>
+      <c r="H177" s="2">
+        <v>0</v>
+      </c>
+      <c r="I177" s="1">
+        <v>46118.795717592591</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B178" t="s">
+        <v>32</v>
+      </c>
+      <c r="C178">
+        <v>2408</v>
+      </c>
+      <c r="D178" t="s">
+        <v>37</v>
+      </c>
+      <c r="F178" t="s">
+        <v>42</v>
+      </c>
+      <c r="G178" t="s">
+        <v>13</v>
+      </c>
+      <c r="H178" s="2">
+        <v>0</v>
+      </c>
+      <c r="I178" s="1">
+        <v>46118.796412037038</v>
+      </c>
+      <c r="J178">
+        <v>1</v>
+      </c>
+      <c r="K178" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B179" t="s">
+        <v>32</v>
+      </c>
+      <c r="C179">
+        <v>2402</v>
+      </c>
+      <c r="D179" t="s">
+        <v>38</v>
+      </c>
+      <c r="F179" t="s">
+        <v>42</v>
+      </c>
+      <c r="G179" t="s">
+        <v>13</v>
+      </c>
+      <c r="H179" s="2">
+        <v>0</v>
+      </c>
+      <c r="I179" s="1">
+        <v>46118.796412037038</v>
+      </c>
+      <c r="J179">
+        <v>1</v>
+      </c>
+      <c r="K179" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B180" t="s">
+        <v>32</v>
+      </c>
+      <c r="C180">
+        <v>2405</v>
+      </c>
+      <c r="D180" t="s">
+        <v>39</v>
+      </c>
+      <c r="F180" t="s">
+        <v>42</v>
+      </c>
+      <c r="G180" t="s">
+        <v>13</v>
+      </c>
+      <c r="H180" s="2">
+        <v>0</v>
+      </c>
+      <c r="I180" s="1">
+        <v>46118.797106481485</v>
+      </c>
+      <c r="J180">
+        <v>1</v>
+      </c>
+      <c r="K180" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B181" t="s">
+        <v>32</v>
+      </c>
+      <c r="C181">
+        <v>2407</v>
+      </c>
+      <c r="D181" t="s">
+        <v>40</v>
+      </c>
+      <c r="F181" t="s">
+        <v>42</v>
+      </c>
+      <c r="G181" t="s">
+        <v>13</v>
+      </c>
+      <c r="H181" s="2">
+        <v>0</v>
+      </c>
+      <c r="I181" s="1">
+        <v>46118.797106481485</v>
+      </c>
+      <c r="J181">
+        <v>1</v>
+      </c>
+      <c r="K181" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B182" t="s">
+        <v>32</v>
+      </c>
+      <c r="C182">
+        <v>2409</v>
+      </c>
+      <c r="D182" t="s">
+        <v>41</v>
+      </c>
+      <c r="F182" t="s">
+        <v>42</v>
+      </c>
+      <c r="G182" t="s">
+        <v>14</v>
+      </c>
+      <c r="H182" s="2">
+        <v>0</v>
+      </c>
+      <c r="I182" s="1">
+        <v>46118.797800925924</v>
+      </c>
+      <c r="J182">
+        <v>1</v>
+      </c>
+      <c r="K182" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H183" s="2"/>
       <c r="I183" s="1"/>
-    </row>
-    <row r="184" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K183" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H184" s="2"/>
       <c r="I184" s="1"/>
     </row>
-    <row r="185" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H185" s="2"/>
       <c r="I185" s="1"/>
     </row>
-    <row r="186" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H186" s="2"/>
       <c r="I186" s="1"/>
     </row>
-    <row r="187" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H187" s="2"/>
       <c r="I187" s="1"/>
     </row>
-    <row r="188" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H188" s="2"/>
       <c r="I188" s="1"/>
     </row>
-    <row r="189" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
     </row>
-    <row r="190" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H190" s="2"/>
       <c r="I190" s="1"/>
     </row>
-    <row r="191" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H191" s="2"/>
       <c r="I191" s="1"/>
     </row>
-    <row r="192" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H192" s="2"/>
       <c r="I192" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Starkey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725C7C66-2828-496B-B976-4D46E8B41A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D46E19B-9EB5-4ECF-B2B4-C023FAEF75F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -5379,7 +5379,7 @@
         <v>46118.794328703705</v>
       </c>
       <c r="J174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K174" t="s">
         <v>11</v>
@@ -5408,7 +5408,7 @@
         <v>46118.795023148145</v>
       </c>
       <c r="J175">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K175" t="s">
         <v>11</v>
@@ -5437,7 +5437,7 @@
         <v>46118.795023148145</v>
       </c>
       <c r="J176">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K176" t="s">
         <v>11</v>
@@ -5466,7 +5466,7 @@
         <v>46118.795717592591</v>
       </c>
       <c r="J177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K177" t="s">
         <v>11</v>
@@ -5495,7 +5495,7 @@
         <v>46118.796412037038</v>
       </c>
       <c r="J178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K178" t="s">
         <v>11</v>
@@ -5524,7 +5524,7 @@
         <v>46118.796412037038</v>
       </c>
       <c r="J179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K179" t="s">
         <v>11</v>
@@ -5553,7 +5553,7 @@
         <v>46118.797106481485</v>
       </c>
       <c r="J180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K180" t="s">
         <v>11</v>
@@ -5582,7 +5582,7 @@
         <v>46118.797106481485</v>
       </c>
       <c r="J181">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K181" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Starkey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D46E19B-9EB5-4ECF-B2B4-C023FAEF75F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638AF899-C3F4-4DEB-90F3-F7AE9E1708F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5379,7 +5379,7 @@
         <v>46118.794328703705</v>
       </c>
       <c r="J174">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K174" t="s">
         <v>11</v>
@@ -5408,7 +5408,7 @@
         <v>46118.795023148145</v>
       </c>
       <c r="J175">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K175" t="s">
         <v>11</v>
@@ -5437,7 +5437,7 @@
         <v>46118.795023148145</v>
       </c>
       <c r="J176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K176" t="s">
         <v>11</v>
@@ -5466,7 +5466,7 @@
         <v>46118.795717592591</v>
       </c>
       <c r="J177">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K177" t="s">
         <v>11</v>
@@ -5495,7 +5495,7 @@
         <v>46118.796412037038</v>
       </c>
       <c r="J178">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K178" t="s">
         <v>11</v>
@@ -5524,7 +5524,7 @@
         <v>46118.796412037038</v>
       </c>
       <c r="J179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K179" t="s">
         <v>11</v>
@@ -5553,7 +5553,7 @@
         <v>46118.797106481485</v>
       </c>
       <c r="J180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K180" t="s">
         <v>11</v>
@@ -5582,7 +5582,7 @@
         <v>46118.797106481485</v>
       </c>
       <c r="J181">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K181" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Starkey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638AF899-C3F4-4DEB-90F3-F7AE9E1708F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB649D0-9DA6-419C-8899-EC909A6E44C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="43">
   <si>
     <t>Company Name</t>
   </si>
@@ -5379,7 +5379,7 @@
         <v>46118.794328703705</v>
       </c>
       <c r="J174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K174" t="s">
         <v>11</v>
@@ -5408,7 +5408,7 @@
         <v>46118.795023148145</v>
       </c>
       <c r="J175">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K175" t="s">
         <v>11</v>
@@ -5437,7 +5437,7 @@
         <v>46118.795023148145</v>
       </c>
       <c r="J176">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K176" t="s">
         <v>11</v>
@@ -5466,7 +5466,7 @@
         <v>46118.795717592591</v>
       </c>
       <c r="J177">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K177" t="s">
         <v>11</v>
@@ -5495,7 +5495,7 @@
         <v>46118.796412037038</v>
       </c>
       <c r="J178">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K178" t="s">
         <v>11</v>
@@ -5524,7 +5524,7 @@
         <v>46118.796412037038</v>
       </c>
       <c r="J179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K179" t="s">
         <v>11</v>
@@ -5553,7 +5553,7 @@
         <v>46118.797106481485</v>
       </c>
       <c r="J180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K180" t="s">
         <v>11</v>
@@ -5582,7 +5582,7 @@
         <v>46118.797106481485</v>
       </c>
       <c r="J181">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K181" t="s">
         <v>11</v>
@@ -5625,40 +5625,265 @@
       </c>
     </row>
     <row r="184" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H184" s="2"/>
-      <c r="I184" s="1"/>
+      <c r="B184" t="s">
+        <v>32</v>
+      </c>
+      <c r="C184">
+        <v>2401</v>
+      </c>
+      <c r="D184" t="s">
+        <v>33</v>
+      </c>
+      <c r="F184" t="s">
+        <v>18</v>
+      </c>
+      <c r="G184" t="s">
+        <v>13</v>
+      </c>
+      <c r="H184" s="2">
+        <v>0</v>
+      </c>
+      <c r="I184" s="1">
+        <v>46146.710069444445</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="185" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H185" s="2"/>
-      <c r="I185" s="1"/>
+      <c r="B185" t="s">
+        <v>32</v>
+      </c>
+      <c r="C185">
+        <v>2403</v>
+      </c>
+      <c r="D185" t="s">
+        <v>34</v>
+      </c>
+      <c r="F185" t="s">
+        <v>18</v>
+      </c>
+      <c r="G185" t="s">
+        <v>13</v>
+      </c>
+      <c r="H185" s="2">
+        <v>0</v>
+      </c>
+      <c r="I185" s="1">
+        <v>46146.710763888892</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="186" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H186" s="2"/>
-      <c r="I186" s="1"/>
+      <c r="B186" t="s">
+        <v>32</v>
+      </c>
+      <c r="C186">
+        <v>2404</v>
+      </c>
+      <c r="D186" t="s">
+        <v>35</v>
+      </c>
+      <c r="F186" t="s">
+        <v>18</v>
+      </c>
+      <c r="G186" t="s">
+        <v>13</v>
+      </c>
+      <c r="H186" s="2">
+        <v>0</v>
+      </c>
+      <c r="I186" s="1">
+        <v>46146.711458333331</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="187" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H187" s="2"/>
-      <c r="I187" s="1"/>
+      <c r="B187" t="s">
+        <v>32</v>
+      </c>
+      <c r="C187">
+        <v>2406</v>
+      </c>
+      <c r="D187" t="s">
+        <v>36</v>
+      </c>
+      <c r="F187" t="s">
+        <v>18</v>
+      </c>
+      <c r="G187" t="s">
+        <v>13</v>
+      </c>
+      <c r="H187" s="2">
+        <v>0</v>
+      </c>
+      <c r="I187" s="1">
+        <v>46146.712152777778</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="188" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H188" s="2"/>
-      <c r="I188" s="1"/>
+      <c r="B188" t="s">
+        <v>32</v>
+      </c>
+      <c r="C188">
+        <v>2408</v>
+      </c>
+      <c r="D188" t="s">
+        <v>37</v>
+      </c>
+      <c r="F188" t="s">
+        <v>18</v>
+      </c>
+      <c r="G188" t="s">
+        <v>13</v>
+      </c>
+      <c r="H188" s="2">
+        <v>0</v>
+      </c>
+      <c r="I188" s="1">
+        <v>46146.712847222225</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="189" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H189" s="2"/>
-      <c r="I189" s="1"/>
+      <c r="B189" t="s">
+        <v>32</v>
+      </c>
+      <c r="C189">
+        <v>2402</v>
+      </c>
+      <c r="D189" t="s">
+        <v>38</v>
+      </c>
+      <c r="F189" t="s">
+        <v>18</v>
+      </c>
+      <c r="G189" t="s">
+        <v>13</v>
+      </c>
+      <c r="H189" s="2">
+        <v>0</v>
+      </c>
+      <c r="I189" s="1">
+        <v>46146.712847222225</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="190" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H190" s="2"/>
-      <c r="I190" s="1"/>
+      <c r="B190" t="s">
+        <v>32</v>
+      </c>
+      <c r="C190">
+        <v>2405</v>
+      </c>
+      <c r="D190" t="s">
+        <v>39</v>
+      </c>
+      <c r="F190" t="s">
+        <v>18</v>
+      </c>
+      <c r="G190" t="s">
+        <v>13</v>
+      </c>
+      <c r="H190" s="2">
+        <v>0</v>
+      </c>
+      <c r="I190" s="1">
+        <v>46146.713541666664</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="191" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H191" s="2"/>
-      <c r="I191" s="1"/>
+      <c r="B191" t="s">
+        <v>32</v>
+      </c>
+      <c r="C191">
+        <v>2407</v>
+      </c>
+      <c r="D191" t="s">
+        <v>40</v>
+      </c>
+      <c r="F191" t="s">
+        <v>18</v>
+      </c>
+      <c r="G191" t="s">
+        <v>13</v>
+      </c>
+      <c r="H191" s="2">
+        <v>0</v>
+      </c>
+      <c r="I191" s="1">
+        <v>46146.714236111111</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="192" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H192" s="2"/>
-      <c r="I192" s="1"/>
+      <c r="B192" t="s">
+        <v>32</v>
+      </c>
+      <c r="C192">
+        <v>2409</v>
+      </c>
+      <c r="D192" t="s">
+        <v>41</v>
+      </c>
+      <c r="F192" t="s">
+        <v>18</v>
+      </c>
+      <c r="G192" t="s">
+        <v>13</v>
+      </c>
+      <c r="H192" s="2">
+        <v>0</v>
+      </c>
+      <c r="I192" s="1">
+        <v>46146.714930555558</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="193" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H193" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Starkey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB649D0-9DA6-419C-8899-EC909A6E44C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F015A108-A479-46F1-8408-BF1CE45264F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -5379,7 +5379,7 @@
         <v>46118.794328703705</v>
       </c>
       <c r="J174">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K174" t="s">
         <v>11</v>
@@ -5408,7 +5408,7 @@
         <v>46118.795023148145</v>
       </c>
       <c r="J175">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K175" t="s">
         <v>11</v>
@@ -5437,7 +5437,7 @@
         <v>46118.795023148145</v>
       </c>
       <c r="J176">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K176" t="s">
         <v>11</v>
@@ -5466,7 +5466,7 @@
         <v>46118.795717592591</v>
       </c>
       <c r="J177">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K177" t="s">
         <v>11</v>
@@ -5495,7 +5495,7 @@
         <v>46118.796412037038</v>
       </c>
       <c r="J178">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K178" t="s">
         <v>11</v>
@@ -5524,7 +5524,7 @@
         <v>46118.796412037038</v>
       </c>
       <c r="J179">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K179" t="s">
         <v>11</v>
@@ -5553,7 +5553,7 @@
         <v>46118.797106481485</v>
       </c>
       <c r="J180">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K180" t="s">
         <v>11</v>
@@ -5582,7 +5582,7 @@
         <v>46118.797106481485</v>
       </c>
       <c r="J181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K181" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Starkey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C488ED-CB3E-4FAD-BD34-C7E57EA9CF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9491C8B-3DAF-4E88-B221-D7B0A9D18325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -5647,7 +5647,7 @@
         <v>46146.710069444445</v>
       </c>
       <c r="J184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K184" t="s">
         <v>11</v>
@@ -5676,7 +5676,7 @@
         <v>46146.710763888892</v>
       </c>
       <c r="J185">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K185" t="s">
         <v>11</v>
@@ -5705,7 +5705,7 @@
         <v>46146.711458333331</v>
       </c>
       <c r="J186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K186" t="s">
         <v>11</v>
@@ -5734,7 +5734,7 @@
         <v>46146.712152777778</v>
       </c>
       <c r="J187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K187" t="s">
         <v>11</v>
@@ -5763,7 +5763,7 @@
         <v>46146.712847222225</v>
       </c>
       <c r="J188">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K188" t="s">
         <v>11</v>
@@ -5792,7 +5792,7 @@
         <v>46146.712847222225</v>
       </c>
       <c r="J189">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K189" t="s">
         <v>11</v>
@@ -5821,7 +5821,7 @@
         <v>46146.713541666664</v>
       </c>
       <c r="J190">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K190" t="s">
         <v>11</v>
@@ -5850,7 +5850,7 @@
         <v>46146.714236111111</v>
       </c>
       <c r="J191">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K191" t="s">
         <v>11</v>
@@ -5879,7 +5879,7 @@
         <v>46146.714930555558</v>
       </c>
       <c r="J192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K192" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Starkey- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Starkey-Trash-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD833C11-92B0-4F8A-A833-00768EE203E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1BFD0E-2EAB-46A0-8128-DB1BA2A32253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5961,7 +5961,7 @@
         <v>46176.430902777778</v>
       </c>
       <c r="J194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K194" t="s">
         <v>11</v>
@@ -5990,7 +5990,7 @@
         <v>46176.431597222225</v>
       </c>
       <c r="J195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K195" t="s">
         <v>11</v>
@@ -6019,7 +6019,7 @@
         <v>46176.431597222225</v>
       </c>
       <c r="J196">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K196" t="s">
         <v>11</v>
@@ -6048,7 +6048,7 @@
         <v>46176.432291666664</v>
       </c>
       <c r="J197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K197" t="s">
         <v>11</v>
@@ -6077,7 +6077,7 @@
         <v>46176.432291666664</v>
       </c>
       <c r="J198">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K198" t="s">
         <v>11</v>
@@ -6106,7 +6106,7 @@
         <v>46176.432986111111</v>
       </c>
       <c r="J199">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K199" t="s">
         <v>11</v>
@@ -6135,7 +6135,7 @@
         <v>46176.432986111111</v>
       </c>
       <c r="J200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K200" t="s">
         <v>11</v>
@@ -6164,7 +6164,7 @@
         <v>46176.432986111111</v>
       </c>
       <c r="J201">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K201" t="s">
         <v>11</v>
